--- a/data/trans_orig/IP16B08-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16B08-Provincia-trans_orig.xlsx
@@ -3203,7 +3203,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,88%</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>14702</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>18479</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36811</t>
+          <t>37227</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>50,66%</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14792</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>32083</t>
+          <t>31677</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
